--- a/data/trans_camb/IP2005-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 12,09</t>
+          <t>-4,45; 12,19</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 16,41</t>
+          <t>-0,09; 17,08</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; 15,08</t>
+          <t>-3,66; 15,98</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,81; 11,16</t>
+          <t>-6,62; 11,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,54; 11,7</t>
+          <t>-8,43; 10,81</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 10,85</t>
+          <t>-12,4; 11,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,13; 9,68</t>
+          <t>-3,42; 9,35</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 11,76</t>
+          <t>-1,88; 11,34</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 9,92</t>
+          <t>-6,26; 8,97</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-4,99; 15,26</t>
+          <t>-5,1; 15,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 20,75</t>
+          <t>-0,08; 21,76</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,35; 19,05</t>
+          <t>-3,76; 20,29</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-10,01; 14,83</t>
+          <t>-7,66; 15,95</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,88; 15,14</t>
+          <t>-9,61; 14,04</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-16,15; 13,93</t>
+          <t>-14,54; 14,73</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 12,22</t>
+          <t>-4,04; 11,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 14,99</t>
+          <t>-2,18; 14,45</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-5,85; 12,7</t>
+          <t>-7,38; 11,34</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,84; 5,68</t>
+          <t>-1,61; 5,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,76; 8,65</t>
+          <t>1,5; 8,21</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,82</t>
+          <t>-2,1; 5,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,79</t>
+          <t>-2,5; 4,12</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,43; 5,0</t>
+          <t>-1,19; 4,99</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,61; 3,22</t>
+          <t>-3,8; 3,32</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,25; 3,61</t>
+          <t>-1,21; 3,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,05; 5,65</t>
+          <t>1,07; 5,58</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,78; 3,39</t>
+          <t>-1,93; 3,29</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,05; 6,69</t>
+          <t>-1,82; 6,8</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>2,0; 10,2</t>
+          <t>1,65; 9,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,33; 6,84</t>
+          <t>-2,37; 6,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 4,29</t>
+          <t>-2,74; 4,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,57; 5,71</t>
+          <t>-1,32; 5,7</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-3,96; 3,71</t>
+          <t>-4,17; 3,79</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,38; 4,15</t>
+          <t>-1,34; 3,98</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,18; 6,51</t>
+          <t>1,19; 6,42</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,01; 3,91</t>
+          <t>-2,15; 3,78</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,55; 3,79</t>
+          <t>-4,83; 3,35</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 5,08</t>
+          <t>-3,3; 4,74</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,64; -6,15</t>
+          <t>-17,09; -6,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,63; 10,06</t>
+          <t>0,6; 9,99</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 8,05</t>
+          <t>-2,37; 7,95</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,17; 2,11</t>
+          <t>-10,0; 1,63</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 5,28</t>
+          <t>-0,73; 5,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,39; 4,84</t>
+          <t>-1,5; 4,73</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,33; -3,98</t>
+          <t>-12,06; -3,62</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,74; 4,08</t>
+          <t>-5,07; 3,62</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-2,9; 5,54</t>
+          <t>-3,34; 5,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,37; -6,55</t>
+          <t>-17,89; -6,64</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 11,53</t>
+          <t>0,67; 11,58</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,31; 9,16</t>
+          <t>-2,52; 9,14</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,79; 2,4</t>
+          <t>-10,89; 1,84</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 5,85</t>
+          <t>-0,78; 6,18</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,46; 5,25</t>
+          <t>-1,59; 5,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-13,08; -4,38</t>
+          <t>-12,78; -3,9</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,26; 4,21</t>
+          <t>-1,24; 4,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,69; 6,89</t>
+          <t>1,89; 7,08</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,39; 1,81</t>
+          <t>-4,15; 1,91</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,56; 4,57</t>
+          <t>-0,73; 4,63</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 4,59</t>
+          <t>-0,6; 4,79</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-4,01; 2,04</t>
+          <t>-3,91; 2,04</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,17; 3,52</t>
+          <t>-0,13; 3,78</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,44; 5,14</t>
+          <t>1,42; 5,18</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,07; 1,2</t>
+          <t>-3,1; 1,3</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 4,85</t>
+          <t>-1,37; 4,76</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>1,88; 7,9</t>
+          <t>2,07; 8,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,86; 2,06</t>
+          <t>-4,63; 2,19</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,22</t>
+          <t>-0,8; 5,28</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,46; 5,22</t>
+          <t>-0,67; 5,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,42; 2,35</t>
+          <t>-4,37; 2,32</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 4,0</t>
+          <t>-0,13; 4,32</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,6; 5,85</t>
+          <t>1,58; 5,9</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,39; 1,36</t>
+          <t>-3,45; 1,48</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 12,19</t>
+          <t>-4,6; 12,8</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,09; 17,08</t>
+          <t>-0,19; 17,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 15,98</t>
+          <t>-4,09; 15,51</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 11,95</t>
+          <t>-7,18; 12,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,43; 10,81</t>
+          <t>-8,88; 11,05</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,4; 11,53</t>
+          <t>-12,92; 10,93</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-3,42; 9,35</t>
+          <t>-2,81; 9,74</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 11,34</t>
+          <t>-1,31; 11,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 8,97</t>
+          <t>-6,91; 9,12</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 15,43</t>
+          <t>-5,25; 16,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 21,76</t>
+          <t>-0,11; 21,91</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 20,29</t>
+          <t>-4,53; 19,88</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,66; 15,95</t>
+          <t>-8,26; 17,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-9,61; 14,04</t>
+          <t>-10,42; 14,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,54; 14,73</t>
+          <t>-15,43; 14,19</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 11,84</t>
+          <t>-3,25; 12,58</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-2,18; 14,45</t>
+          <t>-1,52; 13,87</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 11,34</t>
+          <t>-8,0; 11,5</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,61; 5,79</t>
+          <t>-1,99; 5,29</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,5; 8,21</t>
+          <t>1,67; 8,08</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 5,52</t>
+          <t>-1,99; 5,28</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,5; 4,12</t>
+          <t>-2,53; 4,14</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 4,99</t>
+          <t>-1,72; 4,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,32</t>
+          <t>-3,74; 3,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 3,47</t>
+          <t>-1,15; 3,79</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>1,07; 5,58</t>
+          <t>0,87; 5,56</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 3,29</t>
+          <t>-1,82; 3,21</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 6,8</t>
+          <t>-2,27; 6,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,65; 9,56</t>
+          <t>1,83; 9,43</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 6,43</t>
+          <t>-2,25; 6,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,74; 4,72</t>
+          <t>-2,79; 4,72</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,32; 5,7</t>
+          <t>-1,89; 5,49</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 3,79</t>
+          <t>-4,12; 3,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 3,98</t>
+          <t>-1,3; 4,33</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,19; 6,42</t>
+          <t>1,0; 6,4</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 3,78</t>
+          <t>-2,04; 3,7</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,83; 3,35</t>
+          <t>-4,54; 3,92</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 4,74</t>
+          <t>-2,97; 4,92</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,09; -6,19</t>
+          <t>-17,99; -6,26</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,6; 9,99</t>
+          <t>0,84; 9,55</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,37; 7,95</t>
+          <t>-2,21; 7,34</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 1,63</t>
+          <t>-10,9; 1,97</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 5,69</t>
+          <t>-0,62; 5,31</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,5; 4,73</t>
+          <t>-1,59; 4,71</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,06; -3,62</t>
+          <t>-11,89; -4,16</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-5,07; 3,62</t>
+          <t>-4,72; 4,28</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,34; 5,16</t>
+          <t>-3,08; 5,33</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,89; -6,64</t>
+          <t>-18,68; -6,66</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,67; 11,58</t>
+          <t>0,93; 10,82</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 9,14</t>
+          <t>-2,35; 8,38</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-10,89; 1,84</t>
+          <t>-11,52; 2,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,78; 6,18</t>
+          <t>-0,64; 5,78</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 5,17</t>
+          <t>-1,68; 5,12</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,78; -3,9</t>
+          <t>-12,81; -4,61</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,24; 4,18</t>
+          <t>-1,18; 4,09</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,89; 7,08</t>
+          <t>1,95; 7,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-4,15; 1,91</t>
+          <t>-3,99; 2,08</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 4,63</t>
+          <t>-0,67; 4,46</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,6; 4,79</t>
+          <t>-0,4; 4,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,91; 2,04</t>
+          <t>-3,69; 2,09</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 3,78</t>
+          <t>-0,06; 3,8</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,42; 5,18</t>
+          <t>1,33; 5,24</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,1; 1,3</t>
+          <t>-3,03; 1,46</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,37; 4,76</t>
+          <t>-1,31; 4,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,07; 8,16</t>
+          <t>2,17; 8,08</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,63; 2,19</t>
+          <t>-4,44; 2,38</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 5,28</t>
+          <t>-0,72; 5,07</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 5,45</t>
+          <t>-0,41; 5,35</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,37; 2,32</t>
+          <t>-4,09; 2,47</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,13; 4,32</t>
+          <t>-0,07; 4,37</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,58; 5,9</t>
+          <t>1,47; 5,95</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,45; 1,48</t>
+          <t>-3,37; 1,64</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP2005-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/IP2005-Estudios-trans_camb.xlsx
@@ -529,14 +529,14 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="n"/>
       <c r="F1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="G1" s="3" t="n"/>
@@ -624,32 +624,32 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2,57</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>2,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>-2,57</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
           <t>3,63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>8,67</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>6,29</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>2,57</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>2,06</t>
-        </is>
-      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-1,08</t>
+          <t>4,43</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>2,32</t>
+          <t>0,48</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-4,6; 12,8</t>
+          <t>-8,81; 11,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,19; 17,19</t>
+          <t>-8,54; 11,7</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 15,51</t>
+          <t>-16,13; 9,4</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-7,18; 12,92</t>
+          <t>-4,15; 12,09</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-8,88; 11,05</t>
+          <t>-0,79; 16,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-12,92; 10,93</t>
+          <t>-5,96; 13,89</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 9,74</t>
+          <t>-3,13; 9,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 11,14</t>
+          <t>-2,18; 11,76</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 9,12</t>
+          <t>-7,25; 8,43</t>
         </is>
       </c>
     </row>
@@ -730,32 +730,32 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>3,15%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2,52%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>-3,14%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
           <t>4,31%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr">
         <is>
           <t>10,3%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7,48%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>3,15%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2,52%</t>
-        </is>
-      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-1,32%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>0,58%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-5,25; 16,35</t>
+          <t>-10,01; 14,83</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,11; 21,91</t>
+          <t>-9,88; 15,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-4,53; 19,88</t>
+          <t>-18,8; 12,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 17,21</t>
+          <t>-4,99; 15,26</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-10,42; 14,3</t>
+          <t>-0,9; 20,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-15,43; 14,19</t>
+          <t>-6,43; 17,62</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 12,58</t>
+          <t>-3,68; 12,22</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-1,52; 13,87</t>
+          <t>-2,5; 14,99</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-8,0; 11,5</t>
+          <t>-8,56; 10,76</t>
         </is>
       </c>
     </row>
@@ -840,32 +840,32 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>0,76</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>1,77</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>-0,22</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
           <t>1,91</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr">
         <is>
           <t>4,93</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,59</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0,76</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1,77</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,27</t>
+          <t>0,91</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>0,59</t>
+          <t>0,29</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,29</t>
+          <t>-2,45; 3,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,67; 8,08</t>
+          <t>-1,43; 5,0</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 5,28</t>
+          <t>-3,54; 3,17</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,53; 4,14</t>
+          <t>-1,84; 5,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,72; 4,86</t>
+          <t>1,76; 8,65</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-3,74; 3,1</t>
+          <t>-2,73; 4,93</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 3,79</t>
+          <t>-1,25; 3,61</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,87; 5,56</t>
+          <t>1,05; 5,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-1,82; 3,21</t>
+          <t>-2,07; 3,07</t>
         </is>
       </c>
     </row>
@@ -946,32 +946,32 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>-0,25%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
           <t>2,18%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr">
         <is>
           <t>5,64%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>1,81%</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0,85%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>1,98%</t>
-        </is>
-      </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-0,31%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>0,67%</t>
+          <t>0,33%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 6,16</t>
+          <t>-2,72; 4,29</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,83; 9,43</t>
+          <t>-1,57; 5,71</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 6,14</t>
+          <t>-3,88; 3,61</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,79; 4,72</t>
+          <t>-2,05; 6,69</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 5,49</t>
+          <t>2,0; 10,2</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 3,52</t>
+          <t>-3,07; 5,75</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,33</t>
+          <t>-1,38; 4,15</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1,0; 6,4</t>
+          <t>1,18; 6,51</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-2,04; 3,7</t>
+          <t>-2,3; 3,52</t>
         </is>
       </c>
     </row>
@@ -1056,32 +1056,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>5,14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2,72</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>-4,08</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
           <t>-0,29</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr">
         <is>
           <t>0,93</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>-11,73</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>5,14</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2,72</t>
-        </is>
-      </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-4,15</t>
+          <t>-11,38</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-7,8</t>
+          <t>-7,69</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,54; 3,92</t>
+          <t>0,63; 10,06</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-2,97; 4,92</t>
+          <t>-2,16; 8,05</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-17,99; -6,26</t>
+          <t>-10,02; 2,01</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,84; 9,55</t>
+          <t>-4,55; 3,79</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-2,21; 7,34</t>
+          <t>-2,8; 5,08</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-10,9; 1,97</t>
+          <t>-17,28; -5,74</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-0,62; 5,31</t>
+          <t>-0,59; 5,28</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 4,71</t>
+          <t>-1,39; 4,84</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-11,89; -4,16</t>
+          <t>-12,3; -3,72</t>
         </is>
       </c>
     </row>
@@ -1162,32 +1162,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>-4,47%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
           <t>-0,31%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>0,98%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>-12,39%</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-4,55%</t>
+          <t>-12,02%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-8,39%</t>
+          <t>-8,27%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-4,72; 4,28</t>
+          <t>0,71; 11,53</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 5,33</t>
+          <t>-2,31; 9,16</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-18,68; -6,66</t>
+          <t>-10,67; 2,37</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,93; 10,82</t>
+          <t>-4,74; 4,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-2,35; 8,38</t>
+          <t>-2,9; 5,54</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-11,52; 2,14</t>
+          <t>-18,15; -6,14</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 5,78</t>
+          <t>-0,6; 5,85</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-1,68; 5,12</t>
+          <t>-1,46; 5,25</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-12,81; -4,61</t>
+          <t>-13,0; -4,18</t>
         </is>
       </c>
     </row>
@@ -1272,32 +1272,32 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>1,98</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2,27</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>-0,99</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
           <t>1,5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr">
         <is>
           <t>4,39</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-1,04</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>2,27</t>
-        </is>
-      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-0,92</t>
+          <t>-1,66</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-0,98</t>
+          <t>-1,31</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 4,09</t>
+          <t>-0,56; 4,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,95; 7,03</t>
+          <t>-0,41; 4,59</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-3,99; 2,08</t>
+          <t>-4,15; 1,89</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-0,67; 4,46</t>
+          <t>-1,26; 4,21</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-0,4; 4,68</t>
+          <t>1,69; 6,89</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 2,09</t>
+          <t>-4,85; 1,12</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,06; 3,8</t>
+          <t>-0,17; 3,52</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>1,33; 5,24</t>
+          <t>1,44; 5,14</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-3,03; 1,46</t>
+          <t>-3,35; 0,62</t>
         </is>
       </c>
     </row>
@@ -1378,32 +1378,32 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2,23%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>2,55%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>-1,11%</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
           <t>1,68%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr">
         <is>
           <t>4,94%</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-1,18%</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2,23%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>2,55%</t>
-        </is>
-      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-1,04%</t>
+          <t>-1,87%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-1,1%</t>
+          <t>-1,47%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,66</t>
+          <t>-0,62; 5,22</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2,17; 8,08</t>
+          <t>-0,46; 5,22</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 2,38</t>
+          <t>-4,52; 2,15</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-0,72; 5,07</t>
+          <t>-1,4; 4,85</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-0,41; 5,35</t>
+          <t>1,88; 7,9</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-4,09; 2,47</t>
+          <t>-5,36; 1,28</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 4,37</t>
+          <t>-0,19; 4,0</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>1,47; 5,95</t>
+          <t>1,6; 5,85</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-3,37; 1,64</t>
+          <t>-3,71; 0,73</t>
         </is>
       </c>
     </row>
